--- a/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE copy/stochastic_s3_r5_REINFORCE.xlsx
+++ b/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE copy/stochastic_s3_r5_REINFORCE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Y$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Y$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="178" customWidth="1" min="14" max="14"/>
-    <col width="75" customWidth="1" min="15" max="15"/>
+    <col width="76" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
@@ -2895,8 +2895,5818 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:50:07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/7cf9626a35344f5e8703ea5833cc0f44</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>300</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M30" t="n">
+        <v>16</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>30</v>
+      </c>
+      <c r="R30" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:51:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/6848ac2d6ab743828ea807743c60921e</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>300</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M31" t="n">
+        <v>16</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>30</v>
+      </c>
+      <c r="R31" t="n">
+        <v>100</v>
+      </c>
+      <c r="S31" t="n">
+        <v>100</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>9</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:51:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/6848ac2d6ab743828ea807743c60921e</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>300</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M32" t="n">
+        <v>16</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>30</v>
+      </c>
+      <c r="R32" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:58:45</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/6848ac2d6ab743828ea807743c60921e</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>300</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M33" t="n">
+        <v>16</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>30</v>
+      </c>
+      <c r="R33" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:01:04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/97349e9d148340eea33668187238b7d9</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M34" t="n">
+        <v>16</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" t="n">
+        <v>100</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:04:01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/97349e9d148340eea33668187238b7d9</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>300</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M35" t="n">
+        <v>16</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>30</v>
+      </c>
+      <c r="R35" t="n">
+        <v>100</v>
+      </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:04:01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/97349e9d148340eea33668187238b7d9</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>300</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M36" t="n">
+        <v>16</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>30</v>
+      </c>
+      <c r="R36" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" t="n">
+        <v>100</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:08:03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/97349e9d148340eea33668187238b7d9</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>300</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M37" t="n">
+        <v>16</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R37" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:08:03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/97349e9d148340eea33668187238b7d9</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>300</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>30</v>
+      </c>
+      <c r="R38" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" t="n">
+        <v>100</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>9</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:12:05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/d923e282521c4b758da72029393a8fab</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>300</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>30</v>
+      </c>
+      <c r="R39" t="n">
+        <v>100</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>9</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:12:05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/d923e282521c4b758da72029393a8fab</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>300</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M40" t="n">
+        <v>16</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>30</v>
+      </c>
+      <c r="R40" t="n">
+        <v>100</v>
+      </c>
+      <c r="S40" t="n">
+        <v>100</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>9</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:13:58</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/823f01989e27405883f055c7297a8137</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>300</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L41" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M41" t="n">
+        <v>16</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>30</v>
+      </c>
+      <c r="R41" t="n">
+        <v>100</v>
+      </c>
+      <c r="S41" t="n">
+        <v>100</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>9</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:14:42</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/823f01989e27405883f055c7297a8137</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>300</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M42" t="n">
+        <v>16</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>30</v>
+      </c>
+      <c r="R42" t="n">
+        <v>100</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>9</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:24:48</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e43c1272c7b14bbc88237b311dcf2795</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>300</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M43" t="n">
+        <v>16</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>30</v>
+      </c>
+      <c r="R43" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>9</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:26:47</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/0d511a4a5bcb4b1c91ef59259c21c3b8</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>300</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L44" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M44" t="n">
+        <v>16</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>30</v>
+      </c>
+      <c r="R44" t="n">
+        <v>100</v>
+      </c>
+      <c r="S44" t="n">
+        <v>100</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>9</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:27:55</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/276de6391fea49da846c7989ab9a5561</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>300</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M45" t="n">
+        <v>16</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>30</v>
+      </c>
+      <c r="R45" t="n">
+        <v>100</v>
+      </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>9</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:28:55</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/4da1864b70624384a172de5e90f87fb2</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>300</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M46" t="n">
+        <v>16</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>30</v>
+      </c>
+      <c r="R46" t="n">
+        <v>100</v>
+      </c>
+      <c r="S46" t="n">
+        <v>100</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>9</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:30:23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c482e65c34c04ad2ab891ab1d10c641e</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>300</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M47" t="n">
+        <v>16</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>30</v>
+      </c>
+      <c r="R47" t="n">
+        <v>100</v>
+      </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>9</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:31:33</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/fa147fc7d03244f0ae3bd739bb2017cd</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>300</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L48" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M48" t="n">
+        <v>16</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>30</v>
+      </c>
+      <c r="R48" t="n">
+        <v>100</v>
+      </c>
+      <c r="S48" t="n">
+        <v>100</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>9</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:41:59</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/dfb638b17a2e4bd9b2f30e118996b5eb</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>300</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M49" t="n">
+        <v>16</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>30</v>
+      </c>
+      <c r="R49" t="n">
+        <v>100</v>
+      </c>
+      <c r="S49" t="n">
+        <v>100</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>9</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:42:24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/0e6353f6988a44a29fbc0826ef794f4c</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>300</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M50" t="n">
+        <v>16</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>30</v>
+      </c>
+      <c r="R50" t="n">
+        <v>100</v>
+      </c>
+      <c r="S50" t="n">
+        <v>100</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>9</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:45:06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/22cda7189cdc490eb24bdc83876c92c9</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>300</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M51" t="n">
+        <v>16</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>30</v>
+      </c>
+      <c r="R51" t="n">
+        <v>100</v>
+      </c>
+      <c r="S51" t="n">
+        <v>100</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>9</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:50:04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/8739ed9169304d61a03a6ed76d3ed2b9</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>300</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M52" t="n">
+        <v>16</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>30</v>
+      </c>
+      <c r="R52" t="n">
+        <v>100</v>
+      </c>
+      <c r="S52" t="n">
+        <v>100</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>9</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:51:39</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/1387ccb861364838b9b0f6ae03e24bbe</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>300</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L53" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M53" t="n">
+        <v>16</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>30</v>
+      </c>
+      <c r="R53" t="n">
+        <v>100</v>
+      </c>
+      <c r="S53" t="n">
+        <v>100</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>9</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:52:27</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/f4b01052ebb5422ba300104a343deca4</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>300</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L54" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M54" t="n">
+        <v>16</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>30</v>
+      </c>
+      <c r="R54" t="n">
+        <v>100</v>
+      </c>
+      <c r="S54" t="n">
+        <v>100</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>9</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:53:46</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e2df0770e5dd48b19baced3bc5691cbb</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>300</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L55" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>30</v>
+      </c>
+      <c r="R55" t="n">
+        <v>100</v>
+      </c>
+      <c r="S55" t="n">
+        <v>100</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>9</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:56:41</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/931ba3d392324a7fbc5570bb21c2b2b4</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>300</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L56" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M56" t="n">
+        <v>16</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>30</v>
+      </c>
+      <c r="R56" t="n">
+        <v>100</v>
+      </c>
+      <c r="S56" t="n">
+        <v>100</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:58:39</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/4657b98dc6f74307a22a6e80430d3e52</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>300</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M57" t="n">
+        <v>16</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>30</v>
+      </c>
+      <c r="R57" t="n">
+        <v>100</v>
+      </c>
+      <c r="S57" t="n">
+        <v>100</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>9</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:00:28</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/5fb70caf03de46f4b3bdcfebd4fd2d65</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>300</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M58" t="n">
+        <v>16</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>30</v>
+      </c>
+      <c r="R58" t="n">
+        <v>100</v>
+      </c>
+      <c r="S58" t="n">
+        <v>100</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:02:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/0d1dbcb318674004bbe60d76eabfcfbe</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>300</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M59" t="n">
+        <v>16</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>30</v>
+      </c>
+      <c r="R59" t="n">
+        <v>100</v>
+      </c>
+      <c r="S59" t="n">
+        <v>100</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>9</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:03:26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a6f39427a57b4ca5a3fdd6bc44b3f760</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>300</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L60" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M60" t="n">
+        <v>16</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>30</v>
+      </c>
+      <c r="R60" t="n">
+        <v>100</v>
+      </c>
+      <c r="S60" t="n">
+        <v>100</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>9</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:11:11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a710c2686d984333b03a7fd821771bdb</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>300</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M61" t="n">
+        <v>16</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>30</v>
+      </c>
+      <c r="R61" t="n">
+        <v>100</v>
+      </c>
+      <c r="S61" t="n">
+        <v>100</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:12:36</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c90a1e0078894167a58d914ad24cbc8a</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>300</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M62" t="n">
+        <v>16</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>30</v>
+      </c>
+      <c r="R62" t="n">
+        <v>100</v>
+      </c>
+      <c r="S62" t="n">
+        <v>100</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>9</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:14:01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ea4671a408594dce8299771a9869a46d</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>300</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L63" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M63" t="n">
+        <v>16</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>30</v>
+      </c>
+      <c r="R63" t="n">
+        <v>100</v>
+      </c>
+      <c r="S63" t="n">
+        <v>100</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:14:41</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/27d66688938f47f9bed652aa5955d19b</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>300</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M64" t="n">
+        <v>16</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>30</v>
+      </c>
+      <c r="R64" t="n">
+        <v>100</v>
+      </c>
+      <c r="S64" t="n">
+        <v>100</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>9</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:15:22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/27d66688938f47f9bed652aa5955d19b</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>300</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L65" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M65" t="n">
+        <v>16</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>30</v>
+      </c>
+      <c r="R65" t="n">
+        <v>100</v>
+      </c>
+      <c r="S65" t="n">
+        <v>100</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:15:40</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/db46027b8aaf43dba3793de302575b02</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H66" t="n">
+        <v>300</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L66" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M66" t="n">
+        <v>16</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>30</v>
+      </c>
+      <c r="R66" t="n">
+        <v>100</v>
+      </c>
+      <c r="S66" t="n">
+        <v>100</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>9</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:21:37</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/8559a7885294401785c657465291b4c5</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>300</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L67" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M67" t="n">
+        <v>16</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>30</v>
+      </c>
+      <c r="R67" t="n">
+        <v>100</v>
+      </c>
+      <c r="S67" t="n">
+        <v>100</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>9</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:22:01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/f6ff765107e0462cb3d32ca27994e762</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>300</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L68" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M68" t="n">
+        <v>16</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>30</v>
+      </c>
+      <c r="R68" t="n">
+        <v>100</v>
+      </c>
+      <c r="S68" t="n">
+        <v>100</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>9</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:22:56</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/995b834c2ae64e79b19cf6b813b987b1</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>300</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L69" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M69" t="n">
+        <v>16</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>30</v>
+      </c>
+      <c r="R69" t="n">
+        <v>100</v>
+      </c>
+      <c r="S69" t="n">
+        <v>100</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>9</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:25:38</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/690e0ad27e484ab0ad4801b5661bb8d6</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>300</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L70" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M70" t="n">
+        <v>16</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>30</v>
+      </c>
+      <c r="R70" t="n">
+        <v>100</v>
+      </c>
+      <c r="S70" t="n">
+        <v>100</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>9</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:26:35</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/750fde96f4854d0aa607a8cde39815d8</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H71" t="n">
+        <v>300</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M71" t="n">
+        <v>16</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>30</v>
+      </c>
+      <c r="R71" t="n">
+        <v>100</v>
+      </c>
+      <c r="S71" t="n">
+        <v>100</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>9</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11-30 10:28:49</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/5e47a72df4be4210a61cb8ecdf2b230b</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H72" t="n">
+        <v>300</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L72" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M72" t="n">
+        <v>16</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>30</v>
+      </c>
+      <c r="R72" t="n">
+        <v>100</v>
+      </c>
+      <c r="S72" t="n">
+        <v>100</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>9</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-11-30 19:16:11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e05b637aa74649cdbba9627bb2145f97</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>300</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M73" t="n">
+        <v>16</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>30</v>
+      </c>
+      <c r="R73" t="n">
+        <v>100</v>
+      </c>
+      <c r="S73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>9</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-11-30 19:21:15</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a7e73f47867b4604b9aff8984a45eb48</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H74" t="n">
+        <v>300</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L74" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M74" t="n">
+        <v>16</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>30</v>
+      </c>
+      <c r="R74" t="n">
+        <v>100</v>
+      </c>
+      <c r="S74" t="n">
+        <v>100</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>9</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-11-30 20:03:19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c3b65ae846124709b7a0e0bdb77f6f8c</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H75" t="n">
+        <v>300</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L75" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M75" t="n">
+        <v>16</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>30</v>
+      </c>
+      <c r="R75" t="n">
+        <v>100</v>
+      </c>
+      <c r="S75" t="n">
+        <v>100</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>9</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:50:57</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/30a893ade7a34b82a2d208385e01e9db</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>300</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M76" t="n">
+        <v>16</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>30</v>
+      </c>
+      <c r="R76" t="n">
+        <v>100</v>
+      </c>
+      <c r="S76" t="n">
+        <v>100</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>9</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:52:57</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/3b886bb6729a4f4fa4d572fc4ee4bb3f</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H77" t="n">
+        <v>300</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L77" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M77" t="n">
+        <v>16</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>30</v>
+      </c>
+      <c r="R77" t="n">
+        <v>100</v>
+      </c>
+      <c r="S77" t="n">
+        <v>100</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>9</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:53:33</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/d03102feea644fd29370e19fdfca5b29</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>300</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L78" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M78" t="n">
+        <v>16</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>30</v>
+      </c>
+      <c r="R78" t="n">
+        <v>100</v>
+      </c>
+      <c r="S78" t="n">
+        <v>100</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>9</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:54:01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/848d6eeb0ed74aaa978fd2970dbdc37a</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>300</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L79" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M79" t="n">
+        <v>16</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>30</v>
+      </c>
+      <c r="R79" t="n">
+        <v>100</v>
+      </c>
+      <c r="S79" t="n">
+        <v>100</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>9</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:54:47</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/622e9266924c4bec9aefd336e43c90ed</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>300</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L80" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M80" t="n">
+        <v>16</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>30</v>
+      </c>
+      <c r="R80" t="n">
+        <v>100</v>
+      </c>
+      <c r="S80" t="n">
+        <v>100</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>9</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:56:28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/f52309c2fbdb455ca7159d898c28692e</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H81" t="n">
+        <v>300</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M81" t="n">
+        <v>16</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>30</v>
+      </c>
+      <c r="R81" t="n">
+        <v>100</v>
+      </c>
+      <c r="S81" t="n">
+        <v>100</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>9</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:01:27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/d663a81c85674094ba1862b19b9db5c3</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H82" t="n">
+        <v>300</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L82" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M82" t="n">
+        <v>16</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>30</v>
+      </c>
+      <c r="R82" t="n">
+        <v>100</v>
+      </c>
+      <c r="S82" t="n">
+        <v>100</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>9</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:04:08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/d9e361c235c44636aa8b34c9fabda780</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H83" t="n">
+        <v>300</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L83" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M83" t="n">
+        <v>16</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>30</v>
+      </c>
+      <c r="R83" t="n">
+        <v>100</v>
+      </c>
+      <c r="S83" t="n">
+        <v>100</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>9</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:22:49</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/0bf5877fc9b54869b72b3316a84d0aab</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H84" t="n">
+        <v>300</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L84" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M84" t="n">
+        <v>16</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>30</v>
+      </c>
+      <c r="R84" t="n">
+        <v>100</v>
+      </c>
+      <c r="S84" t="n">
+        <v>100</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>9</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:40:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/9379439880ac4d5bb2c341aab87eca62</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H85" t="n">
+        <v>300</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L85" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M85" t="n">
+        <v>16</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>30</v>
+      </c>
+      <c r="R85" t="n">
+        <v>100</v>
+      </c>
+      <c r="S85" t="n">
+        <v>100</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>9</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:41:52</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ed46fb515076411ea7427dadefdfbe02</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H86" t="n">
+        <v>300</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M86" t="n">
+        <v>16</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>30</v>
+      </c>
+      <c r="R86" t="n">
+        <v>100</v>
+      </c>
+      <c r="S86" t="n">
+        <v>100</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>9</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:47:30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/bce98ad8a1fa4b5a954db4f734a80e5f</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H87" t="n">
+        <v>300</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M87" t="n">
+        <v>16</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>30</v>
+      </c>
+      <c r="R87" t="n">
+        <v>100</v>
+      </c>
+      <c r="S87" t="n">
+        <v>100</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>9</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:50:42</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/b39ef20dd2c94b6c9fe48724e54ff70c</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>300</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M88" t="n">
+        <v>16</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>30</v>
+      </c>
+      <c r="R88" t="n">
+        <v>100</v>
+      </c>
+      <c r="S88" t="n">
+        <v>100</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>9</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:03:13</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e7e6de837d8448b28876eddbf96a746b</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H89" t="n">
+        <v>300</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L89" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M89" t="n">
+        <v>16</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>30</v>
+      </c>
+      <c r="R89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S89" t="n">
+        <v>100</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>9</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:04:03</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/69a2b1c4f769404fa9783181e8786ed2</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>300</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L90" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M90" t="n">
+        <v>16</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>30</v>
+      </c>
+      <c r="R90" t="n">
+        <v>100</v>
+      </c>
+      <c r="S90" t="n">
+        <v>100</v>
+      </c>
+      <c r="T90" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
+        <v>9</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:04:29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e85bb8fc2c54459b9684006726833e5f</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>300</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L91" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M91" t="n">
+        <v>16</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>30</v>
+      </c>
+      <c r="R91" t="n">
+        <v>100</v>
+      </c>
+      <c r="S91" t="n">
+        <v>100</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>9</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:06:24</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/30bcaf5ec4b54352981ca9fb3743122f</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H92" t="n">
+        <v>300</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L92" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M92" t="n">
+        <v>16</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>30</v>
+      </c>
+      <c r="R92" t="n">
+        <v>100</v>
+      </c>
+      <c r="S92" t="n">
+        <v>100</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>9</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:07:34</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/74a11a81026448d1be338bd34535f971</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H93" t="n">
+        <v>300</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L93" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M93" t="n">
+        <v>16</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>30</v>
+      </c>
+      <c r="R93" t="n">
+        <v>100</v>
+      </c>
+      <c r="S93" t="n">
+        <v>100</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>9</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:09:57</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a861b24acd0e4497a6208c5522eb225f</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H94" t="n">
+        <v>300</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L94" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M94" t="n">
+        <v>16</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>30</v>
+      </c>
+      <c r="R94" t="n">
+        <v>100</v>
+      </c>
+      <c r="S94" t="n">
+        <v>100</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>9</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:10:17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a248b30fbbea4edb9bd1f573b77b7254</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H95" t="n">
+        <v>300</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L95" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M95" t="n">
+        <v>16</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>30</v>
+      </c>
+      <c r="R95" t="n">
+        <v>100</v>
+      </c>
+      <c r="S95" t="n">
+        <v>100</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>9</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:12:02</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/02e4b8b08c6d41c082e2593d560878a7</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>300</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L96" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M96" t="n">
+        <v>16</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>30</v>
+      </c>
+      <c r="R96" t="n">
+        <v>100</v>
+      </c>
+      <c r="S96" t="n">
+        <v>100</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>9</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:14:01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c4ec6cd1fe9e41e7bbeb97427940a965</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H97" t="n">
+        <v>300</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L97" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M97" t="n">
+        <v>16</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>30</v>
+      </c>
+      <c r="R97" t="n">
+        <v>100</v>
+      </c>
+      <c r="S97" t="n">
+        <v>100</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>9</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:15:42</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/fcca5c4c57624e66a088e4017bc9001f</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>300</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L98" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M98" t="n">
+        <v>16</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>30</v>
+      </c>
+      <c r="R98" t="n">
+        <v>100</v>
+      </c>
+      <c r="S98" t="n">
+        <v>100</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>9</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:17:59</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ca6c2b5bcf9b4fd5a8e97583da71a30a</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H99" t="n">
+        <v>300</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L99" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M99" t="n">
+        <v>16</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>30</v>
+      </c>
+      <c r="R99" t="n">
+        <v>100</v>
+      </c>
+      <c r="S99" t="n">
+        <v>100</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>9</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y29"/>
+  <autoFilter ref="A1:Y99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE copy/stochastic_s3_r5_REINFORCE.xlsx
+++ b/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE copy/stochastic_s3_r5_REINFORCE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Y$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Y$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8705,8 +8705,3079 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-12-01 13:47:02</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/2e0d73a8c18340adaa7d7f2d28c000be</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>300</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L100" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M100" t="n">
+        <v>8</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>30</v>
+      </c>
+      <c r="R100" t="n">
+        <v>100</v>
+      </c>
+      <c r="S100" t="n">
+        <v>100</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>9</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-12-01 13:51:24</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/9d1a6e9d79734381a5a2782acef41e1a</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H101" t="n">
+        <v>300</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L101" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M101" t="n">
+        <v>8</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>30</v>
+      </c>
+      <c r="R101" t="n">
+        <v>100</v>
+      </c>
+      <c r="S101" t="n">
+        <v>100</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>9</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-12-01 13:54:21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/092cf6b8e93f488e8ab8ba89184014d4</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>300</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M102" t="n">
+        <v>8</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>30</v>
+      </c>
+      <c r="R102" t="n">
+        <v>100</v>
+      </c>
+      <c r="S102" t="n">
+        <v>100</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>9</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-12-01 13:58:33</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/4d15603df9b44c88917db489628d88eb</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H103" t="n">
+        <v>300</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L103" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M103" t="n">
+        <v>16</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>30</v>
+      </c>
+      <c r="R103" t="n">
+        <v>100</v>
+      </c>
+      <c r="S103" t="n">
+        <v>100</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>9</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-12-01 14:25:52</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/cc4d689bbddf4a3abf37168de3dd9431</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H104" t="n">
+        <v>300</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 320)</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L104" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M104" t="n">
+        <v>16</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>30</v>
+      </c>
+      <c r="R104" t="n">
+        <v>100</v>
+      </c>
+      <c r="S104" t="n">
+        <v>100</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>9</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-12-01 14:29:11</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ef39677d29d1438c8e405d61bd18e611</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H105" t="n">
+        <v>300</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>5</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L105" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>30</v>
+      </c>
+      <c r="R105" t="n">
+        <v>100</v>
+      </c>
+      <c r="S105" t="n">
+        <v>100</v>
+      </c>
+      <c r="T105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>9</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-12-01 14:31:43</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/fa168035f3e44a4391989db8697ac933</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H106" t="n">
+        <v>300</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L106" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M106" t="n">
+        <v>4</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>30</v>
+      </c>
+      <c r="R106" t="n">
+        <v>100</v>
+      </c>
+      <c r="S106" t="n">
+        <v>100</v>
+      </c>
+      <c r="T106" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>9</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:24:45</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e22de6bfb7e24c349449aa68b3c51b1e</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>300</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L107" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M107" t="n">
+        <v>4</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>30</v>
+      </c>
+      <c r="R107" t="n">
+        <v>100</v>
+      </c>
+      <c r="S107" t="n">
+        <v>100</v>
+      </c>
+      <c r="T107" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" t="n">
+        <v>9</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:29:43</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/2ae006eb0b2b489fad8b037b2d98c95f</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>300</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L108" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M108" t="n">
+        <v>4</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>30</v>
+      </c>
+      <c r="R108" t="n">
+        <v>100</v>
+      </c>
+      <c r="S108" t="n">
+        <v>100</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>9</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:30:25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a2b2d8fd8c2e42ca840930f703b6ad9f</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H109" t="n">
+        <v>300</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L109" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M109" t="n">
+        <v>4</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>30</v>
+      </c>
+      <c r="R109" t="n">
+        <v>100</v>
+      </c>
+      <c r="S109" t="n">
+        <v>100</v>
+      </c>
+      <c r="T109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>9</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:30:47</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/1746e76c66124bbe9ba03cd181b3c062</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H110" t="n">
+        <v>300</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L110" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>30</v>
+      </c>
+      <c r="R110" t="n">
+        <v>100</v>
+      </c>
+      <c r="S110" t="n">
+        <v>100</v>
+      </c>
+      <c r="T110" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" t="n">
+        <v>9</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:33:13</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/515e998ee86a48ab8ba0097ad4975c11</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>300</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L111" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M111" t="n">
+        <v>4</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>30</v>
+      </c>
+      <c r="R111" t="n">
+        <v>100</v>
+      </c>
+      <c r="S111" t="n">
+        <v>100</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="n">
+        <v>9</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:33:25</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/e48015d9c3d244ff90513c9fc20cc847</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>300</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>5</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L112" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M112" t="n">
+        <v>4</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>30</v>
+      </c>
+      <c r="R112" t="n">
+        <v>100</v>
+      </c>
+      <c r="S112" t="n">
+        <v>100</v>
+      </c>
+      <c r="T112" t="n">
+        <v>1</v>
+      </c>
+      <c r="U112" t="n">
+        <v>9</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:51:20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/7b9a5000d5bf4fe0a68d3801c13da703</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>300</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>5</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L113" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M113" t="n">
+        <v>4</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>30</v>
+      </c>
+      <c r="R113" t="n">
+        <v>100</v>
+      </c>
+      <c r="S113" t="n">
+        <v>100</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1</v>
+      </c>
+      <c r="U113" t="n">
+        <v>9</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:52:52</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/30b5a5a15f624881abd78f80091b21f3</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>300</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L114" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M114" t="n">
+        <v>4</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>30</v>
+      </c>
+      <c r="R114" t="n">
+        <v>100</v>
+      </c>
+      <c r="S114" t="n">
+        <v>100</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" t="n">
+        <v>9</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:54:50</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/559cc8d9a5b542af97092b25635423e9</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H115" t="n">
+        <v>300</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>5</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L115" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M115" t="n">
+        <v>4</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>30</v>
+      </c>
+      <c r="R115" t="n">
+        <v>100</v>
+      </c>
+      <c r="S115" t="n">
+        <v>100</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>9</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:00:54</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ef973ae4c04b485fb8964c789c7fa6d3</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H116" t="n">
+        <v>300</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L116" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M116" t="n">
+        <v>4</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>30</v>
+      </c>
+      <c r="R116" t="n">
+        <v>100</v>
+      </c>
+      <c r="S116" t="n">
+        <v>100</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="n">
+        <v>9</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:01:30</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/91e5826a96ee4d918b0dfde7fa3f3289</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>300</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L117" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M117" t="n">
+        <v>4</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>30</v>
+      </c>
+      <c r="R117" t="n">
+        <v>100</v>
+      </c>
+      <c r="S117" t="n">
+        <v>100</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" t="n">
+        <v>9</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:02:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/b56b9c6cbcf341daba4241fc44c45448</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>300</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>5</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L118" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>30</v>
+      </c>
+      <c r="R118" t="n">
+        <v>100</v>
+      </c>
+      <c r="S118" t="n">
+        <v>100</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" t="n">
+        <v>9</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:04:33</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/51a82e8642b741aabbe7d5f4bea7a010</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>300</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L119" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M119" t="n">
+        <v>4</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>30</v>
+      </c>
+      <c r="R119" t="n">
+        <v>100</v>
+      </c>
+      <c r="S119" t="n">
+        <v>100</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>9</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:04:58</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/2bb214f7da2a47b08e0a3bb5c361f7de</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>300</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L120" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>30</v>
+      </c>
+      <c r="R120" t="n">
+        <v>100</v>
+      </c>
+      <c r="S120" t="n">
+        <v>100</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
+        <v>9</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:06:08</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/b9f3374b7582430cbc3627a8ad07a733</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>300</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>5</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L121" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>30</v>
+      </c>
+      <c r="R121" t="n">
+        <v>100</v>
+      </c>
+      <c r="S121" t="n">
+        <v>100</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>9</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:23:59</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/646a8596dc4d46aca2cb4c34a95c00d1</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>300</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L122" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M122" t="n">
+        <v>4</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>30</v>
+      </c>
+      <c r="R122" t="n">
+        <v>100</v>
+      </c>
+      <c r="S122" t="n">
+        <v>100</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" t="n">
+        <v>9</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:27:32</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/4227223d562b426dacb7d53f75983275</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H123" t="n">
+        <v>300</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L123" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M123" t="n">
+        <v>4</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>30</v>
+      </c>
+      <c r="R123" t="n">
+        <v>100</v>
+      </c>
+      <c r="S123" t="n">
+        <v>100</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" t="n">
+        <v>9</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-12-01 18:12:17</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/7f4e7c1e03c34182a5271dfeef81f645</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>300</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L124" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M124" t="n">
+        <v>4</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>30</v>
+      </c>
+      <c r="R124" t="n">
+        <v>100</v>
+      </c>
+      <c r="S124" t="n">
+        <v>100</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" t="n">
+        <v>9</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-12-01 21:29:20</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/5fa743b8498c42c9b05a4fe148e3f155</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>300</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L125" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M125" t="n">
+        <v>4</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>30</v>
+      </c>
+      <c r="R125" t="n">
+        <v>100</v>
+      </c>
+      <c r="S125" t="n">
+        <v>100</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>9</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:52:32</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ce6b87d5304942969864d7b29e573795</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>300</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>5</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L126" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>30</v>
+      </c>
+      <c r="R126" t="n">
+        <v>100</v>
+      </c>
+      <c r="S126" t="n">
+        <v>100</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" t="n">
+        <v>9</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:59:54</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/f6849bad050c40dcac5ad9b391e47a89</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>300</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L127" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M127" t="n">
+        <v>4</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>30</v>
+      </c>
+      <c r="R127" t="n">
+        <v>100</v>
+      </c>
+      <c r="S127" t="n">
+        <v>100</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="n">
+        <v>9</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-12-02 18:41:36</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/1d18a9eaf9d4499ba5ba13c05f4bdc09</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H128" t="n">
+        <v>300</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L128" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>30</v>
+      </c>
+      <c r="R128" t="n">
+        <v>100</v>
+      </c>
+      <c r="S128" t="n">
+        <v>100</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" t="n">
+        <v>9</v>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-12-03 09:18:46</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/fd1eb1881b77429db1ab9e255336cb74</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>300</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L129" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M129" t="n">
+        <v>4</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>30</v>
+      </c>
+      <c r="R129" t="n">
+        <v>100</v>
+      </c>
+      <c r="S129" t="n">
+        <v>100</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="n">
+        <v>9</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-12-03 09:28:11</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/a2c283e068544a6dbf82a34690f4e5bd</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>300</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M130" t="n">
+        <v>4</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>30</v>
+      </c>
+      <c r="R130" t="n">
+        <v>100</v>
+      </c>
+      <c r="S130" t="n">
+        <v>100</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" t="n">
+        <v>9</v>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-12-03 09:37:44</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/db882c6237794882bae49b87b4019300</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H131" t="n">
+        <v>300</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L131" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M131" t="n">
+        <v>4</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>30</v>
+      </c>
+      <c r="R131" t="n">
+        <v>100</v>
+      </c>
+      <c r="S131" t="n">
+        <v>100</v>
+      </c>
+      <c r="T131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>9</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-12-03 09:50:36</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c9f94e38dd974c79bcee3a06cc8ab2fc</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>300</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L132" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M132" t="n">
+        <v>4</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>30</v>
+      </c>
+      <c r="R132" t="n">
+        <v>100</v>
+      </c>
+      <c r="S132" t="n">
+        <v>100</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>9</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:05:07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/1c08ad16ada14308ba25dfb8e11d139b</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H133" t="n">
+        <v>300</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>5</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L133" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M133" t="n">
+        <v>4</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>30</v>
+      </c>
+      <c r="R133" t="n">
+        <v>100</v>
+      </c>
+      <c r="S133" t="n">
+        <v>100</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" t="n">
+        <v>9</v>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:53:14</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/ba29bdb78dda4f728632bbc8131b7e15</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>300</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L134" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>30</v>
+      </c>
+      <c r="R134" t="n">
+        <v>100</v>
+      </c>
+      <c r="S134" t="n">
+        <v>100</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>9</v>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:54:21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/c9fbc9f428c644bda993bc5106a53659</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>300</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L135" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M135" t="n">
+        <v>4</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>30</v>
+      </c>
+      <c r="R135" t="n">
+        <v>100</v>
+      </c>
+      <c r="S135" t="n">
+        <v>100</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>9</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-12-03 12:53:55</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce/11abc813f56e4cdaaa9961a41e7f8206</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>300</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>(5, 3, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>5</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L136" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M136" t="n">
+        <v>4</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>30</v>
+      </c>
+      <c r="R136" t="n">
+        <v>100</v>
+      </c>
+      <c r="S136" t="n">
+        <v>100</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" t="n">
+        <v>9</v>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>{'structure': 1.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.35679185088982296), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y99"/>
+  <autoFilter ref="A1:Y136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>